--- a/Produkty/463-50060463.xlsx
+++ b/Produkty/463-50060463.xlsx
@@ -445,7 +445,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>570x60x28-463</v>
+        <v>570x60x28</v>
       </c>
       <c r="C2" t="str">
         <v>570</v>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>630x60x28-463</v>
+        <v>630x60x28</v>
       </c>
       <c r="C3" t="str">
         <v>630</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>570x40x28-463</v>
+        <v>570x40x28</v>
       </c>
       <c r="C4" t="str">
         <v>570</v>
